--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N41_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N41_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1.328370393088669</v>
+        <v>0.2158601888769088</v>
       </c>
       <c r="D2" t="n">
-        <v>1.330599048233717</v>
+        <v>0.216222345337979</v>
       </c>
       <c r="E2" t="n">
-        <v>11.88597180058631</v>
+        <v>1.931470417595276</v>
       </c>
       <c r="F2" t="n">
-        <v>13.90032683943669</v>
+        <v>2.258803111408462</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.86491103243126</v>
+        <v>3.715548042770079</v>
       </c>
       <c r="D3" t="n">
-        <v>22.86402825640156</v>
+        <v>3.715404591665253</v>
       </c>
       <c r="E3" t="n">
-        <v>11.88597180058631</v>
+        <v>1.931470417595276</v>
       </c>
       <c r="F3" t="n">
-        <v>13.90032683943669</v>
+        <v>2.258803111408462</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.25611427219982</v>
+        <v>5.07911856923247</v>
       </c>
       <c r="D4" t="n">
-        <v>31.09322077677806</v>
+        <v>5.052648376226435</v>
       </c>
       <c r="E4" t="n">
-        <v>11.88597180058631</v>
+        <v>1.931470417595276</v>
       </c>
       <c r="F4" t="n">
-        <v>13.90032683943669</v>
+        <v>2.258803111408462</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.57701826018281</v>
+        <v>3.993765467279706</v>
       </c>
       <c r="D5" t="n">
-        <v>23.88880730856819</v>
+        <v>3.881931187642331</v>
       </c>
       <c r="E5" t="n">
-        <v>11.88597180058631</v>
+        <v>1.931470417595276</v>
       </c>
       <c r="F5" t="n">
-        <v>13.90032683943669</v>
+        <v>2.258803111408462</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>43.68139462186516</v>
+        <v>7.098226626053089</v>
       </c>
       <c r="D6" t="n">
-        <v>40.94203219186854</v>
+        <v>6.653080231178638</v>
       </c>
       <c r="E6" t="n">
-        <v>11.88597180058631</v>
+        <v>1.931470417595276</v>
       </c>
       <c r="F6" t="n">
-        <v>13.90032683943669</v>
+        <v>2.258803111408462</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>45.51079640326254</v>
+        <v>7.395504415530163</v>
       </c>
       <c r="D7" t="n">
-        <v>21.22498527679112</v>
+        <v>3.449060107478558</v>
       </c>
       <c r="E7" t="n">
-        <v>11.88597180058631</v>
+        <v>1.931470417595276</v>
       </c>
       <c r="F7" t="n">
-        <v>13.90032683943669</v>
+        <v>2.258803111408462</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>25.58112092824376</v>
+        <v>4.15693215083961</v>
       </c>
       <c r="D8" t="n">
-        <v>25.91629717056044</v>
+        <v>4.211398290216072</v>
       </c>
       <c r="E8" t="n">
-        <v>11.88597180058631</v>
+        <v>1.931470417595276</v>
       </c>
       <c r="F8" t="n">
-        <v>13.90032683943669</v>
+        <v>2.258803111408462</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>48.53758924219913</v>
+        <v>7.88735825185736</v>
       </c>
       <c r="D9" t="n">
-        <v>48.68663070984212</v>
+        <v>7.911577490349345</v>
       </c>
       <c r="E9" t="n">
-        <v>11.88597180058631</v>
+        <v>1.931470417595276</v>
       </c>
       <c r="F9" t="n">
-        <v>13.90032683943669</v>
+        <v>2.258803111408462</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>53.07641569263864</v>
+        <v>8.62491755005378</v>
       </c>
       <c r="D10" t="n">
-        <v>48.32245291735544</v>
+        <v>7.852398599070259</v>
       </c>
       <c r="E10" t="n">
-        <v>11.88597180058631</v>
+        <v>1.931470417595276</v>
       </c>
       <c r="F10" t="n">
-        <v>13.90032683943669</v>
+        <v>2.258803111408462</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>36.33298100896639</v>
+        <v>5.904109413957039</v>
       </c>
       <c r="D11" t="n">
-        <v>21.74782917750752</v>
+        <v>3.534022241344973</v>
       </c>
       <c r="E11" t="n">
-        <v>11.88597180058631</v>
+        <v>1.931470417595276</v>
       </c>
       <c r="F11" t="n">
-        <v>13.90032683943669</v>
+        <v>2.258803111408462</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>39.39638817961107</v>
+        <v>6.401913079186798</v>
       </c>
       <c r="D12" t="n">
-        <v>35.63469167569474</v>
+        <v>5.790637397300396</v>
       </c>
       <c r="E12" t="n">
-        <v>11.88597180058631</v>
+        <v>1.931470417595276</v>
       </c>
       <c r="F12" t="n">
-        <v>13.90032683943669</v>
+        <v>2.258803111408462</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>45.58026609834975</v>
+        <v>7.406793240981835</v>
       </c>
       <c r="D13" t="n">
-        <v>55.3540731134548</v>
+        <v>8.995036880936405</v>
       </c>
       <c r="E13" t="n">
-        <v>11.88597180058631</v>
+        <v>1.931470417595276</v>
       </c>
       <c r="F13" t="n">
-        <v>13.90032683943669</v>
+        <v>2.258803111408462</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>30.49189567159762</v>
+        <v>4.954933046634613</v>
       </c>
       <c r="D14" t="n">
-        <v>40.94629653020864</v>
+        <v>6.653773186158904</v>
       </c>
       <c r="E14" t="n">
-        <v>11.88597180058631</v>
+        <v>1.931470417595276</v>
       </c>
       <c r="F14" t="n">
-        <v>13.90032683943669</v>
+        <v>2.258803111408462</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>29.66812314360646</v>
+        <v>4.821070010836049</v>
       </c>
       <c r="D15" t="n">
-        <v>46.64397654647158</v>
+        <v>7.579646188801632</v>
       </c>
       <c r="E15" t="n">
-        <v>11.88597180058631</v>
+        <v>1.931470417595276</v>
       </c>
       <c r="F15" t="n">
-        <v>13.90032683943669</v>
+        <v>2.258803111408462</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>31.64327028503062</v>
+        <v>5.142031421317476</v>
       </c>
       <c r="D16" t="n">
-        <v>23.86266208041918</v>
+        <v>3.877682588068116</v>
       </c>
       <c r="E16" t="n">
-        <v>11.88597180058631</v>
+        <v>1.931470417595276</v>
       </c>
       <c r="F16" t="n">
-        <v>13.90032683943669</v>
+        <v>2.258803111408462</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>28.1159477722576</v>
+        <v>4.56884151299186</v>
       </c>
       <c r="D17" t="n">
-        <v>17</v>
+        <v>2.7625</v>
       </c>
       <c r="E17" t="n">
-        <v>11.88597180058631</v>
+        <v>1.931470417595276</v>
       </c>
       <c r="F17" t="n">
-        <v>13.90032683943669</v>
+        <v>2.258803111408462</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>29.7637497064628</v>
+        <v>4.836609327300205</v>
       </c>
       <c r="D18" t="n">
-        <v>14.80709289496085</v>
+        <v>2.406152595431138</v>
       </c>
       <c r="E18" t="n">
-        <v>11.88597180058631</v>
+        <v>1.931470417595276</v>
       </c>
       <c r="F18" t="n">
-        <v>13.90032683943669</v>
+        <v>2.258803111408462</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>21.57204703977316</v>
+        <v>3.505457643963139</v>
       </c>
       <c r="D19" t="n">
-        <v>20.4473295801824</v>
+        <v>3.32269105677964</v>
       </c>
       <c r="E19" t="n">
-        <v>11.88597180058631</v>
+        <v>1.931470417595276</v>
       </c>
       <c r="F19" t="n">
-        <v>13.90032683943669</v>
+        <v>2.258803111408462</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
